--- a/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -471,19 +471,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:G8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.424911" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.996339" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19.710625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="21.424911" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="12.424911" customWidth="1"/>
+    <x:col min="3" max="3" width="9.424911" customWidth="1"/>
+    <x:col min="4" max="4" width="12.996339" customWidth="1"/>
+    <x:col min="5" max="5" width="19.710625" customWidth="1"/>
+    <x:col min="6" max="6" width="21.424911" customWidth="1"/>
+    <x:col min="7" max="7" width="20.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:7">
@@ -527,16 +524,16 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
-      <x:c r="B4" s="0" t="b">
+      <x:c r="B4" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="b">
+      <x:c r="C4" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="b">
+      <x:c r="D4" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="b">
+      <x:c r="E4" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
@@ -550,13 +547,13 @@
       <x:c r="B5" s="5">
         <x:v>1234.567</x:v>
       </x:c>
-      <x:c r="C5" s="0">
+      <x:c r="C5">
         <x:v>1234.567</x:v>
       </x:c>
-      <x:c r="D5" s="0">
+      <x:c r="D5">
         <x:v>1234.567</x:v>
       </x:c>
-      <x:c r="E5" s="0">
+      <x:c r="E5">
         <x:v>1234.567</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
@@ -567,22 +564,22 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="D6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E6" s="0" t="s">
+      <x:c r="E6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="F6" s="0" t="s">
+      <x:c r="F6" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G6" s="0" t="s">
+      <x:c r="G6" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
@@ -607,16 +604,16 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
-      <x:c r="B8" s="0" t="e">
+      <x:c r="B8" t="e">
         <x:v>#DIV/0!</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="e">
+      <x:c r="C8" t="e">
         <x:v>#DIV/0!</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="e">
+      <x:c r="D8" t="e">
         <x:v>#DIV/0!</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="e">
+      <x:c r="E8" t="e">
         <x:v>#DIV/0!</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
@@ -627,19 +624,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -649,98 +639,87 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:C9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="2" spans="1:3">
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="B3" s="0" t="e">
+      <x:c r="B3" t="e">
         <x:v>#REF!</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="e">
+      <x:c r="C3" t="e">
         <x:f>#REF!+1</x:f>
         <x:v>#REF!</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="B4" s="0" t="e">
+      <x:c r="B4" t="e">
         <x:v>#VALUE!</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="e">
+      <x:c r="C4" t="e">
         <x:f>"TRUE"*1</x:f>
         <x:v>#VALUE!</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="B5" s="0" t="e">
+      <x:c r="B5" t="e">
         <x:v>#DIV/0!</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="e">
+      <x:c r="C5" t="e">
         <x:f>1/0</x:f>
         <x:v>#DIV/0!</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="B6" s="0" t="e">
+      <x:c r="B6" t="e">
         <x:v>#NAME?</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="e">
+      <x:c r="C6" t="e">
         <x:f>NONEXISTENT.FUNCTION()</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="B7" s="0" t="e">
+      <x:c r="B7" t="e">
         <x:v>#N/A</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="e">
+      <x:c r="C7" t="e">
         <x:f>NA()</x:f>
         <x:v>#N/A</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="B8" s="0" t="e">
+      <x:c r="B8" t="e">
         <x:v>#NULL!</x:v>
       </x:c>
-      <x:c r="C8" s="0" t="e">
+      <x:c r="C8" t="e">
         <x:f>#NULL!+1</x:f>
         <x:v>#NULL!</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
-      <x:c r="B9" s="0" t="e">
+      <x:c r="B9" t="e">
         <x:v>#NUM!</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="e">
+      <x:c r="C9" t="e">
         <x:f>#NUM!+1</x:f>
         <x:v>#NUM!</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -585,16 +585,16 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="B7" s="6">
-        <x:v>1.10538194444444</x:v>
+        <x:v>1.1053819444444444</x:v>
       </x:c>
       <x:c r="C7" s="6">
-        <x:v>1.10538194444444</x:v>
+        <x:v>1.1053819444444444</x:v>
       </x:c>
       <x:c r="D7" s="6">
-        <x:v>1.10538194444444</x:v>
+        <x:v>1.1053819444444444</x:v>
       </x:c>
       <x:c r="E7" s="6">
-        <x:v>1.10538194444444</x:v>
+        <x:v>1.1053819444444444</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
         <x:v>12</x:v>

--- a/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -475,12 +475,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="12.424911" customWidth="1"/>
-    <x:col min="3" max="3" width="9.424911" customWidth="1"/>
-    <x:col min="4" max="4" width="12.996339" customWidth="1"/>
-    <x:col min="5" max="5" width="19.710625" customWidth="1"/>
-    <x:col min="6" max="6" width="21.424911" customWidth="1"/>
-    <x:col min="7" max="7" width="20.710625" customWidth="1"/>
+    <x:col min="2" max="2" width="11.853482" customWidth="1"/>
+    <x:col min="3" max="3" width="9.139196" customWidth="1"/>
+    <x:col min="4" max="4" width="12.424911" customWidth="1"/>
+    <x:col min="5" max="5" width="19.139196" customWidth="1"/>
+    <x:col min="6" max="6" width="20.853482" customWidth="1"/>
+    <x:col min="7" max="7" width="20.139196" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:7">

--- a/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -474,13 +474,13 @@
   <x:dimension ref="A1:G8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="11.853482" customWidth="1"/>
-    <x:col min="3" max="3" width="9.139196" customWidth="1"/>
-    <x:col min="4" max="4" width="12.424911" customWidth="1"/>
-    <x:col min="5" max="5" width="19.139196" customWidth="1"/>
-    <x:col min="6" max="6" width="20.853482" customWidth="1"/>
-    <x:col min="7" max="7" width="20.139196" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="11.857143" customWidth="1"/>
+    <x:col min="3" max="3" width="9.142857" customWidth="1"/>
+    <x:col min="4" max="4" width="12.428571" customWidth="1"/>
+    <x:col min="5" max="5" width="19.142857" customWidth="1"/>
+    <x:col min="6" max="6" width="20.857143" customWidth="1"/>
+    <x:col min="7" max="7" width="20.142857" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:7">
